--- a/Apostas_Diarias/Apostas_20260420.xlsx
+++ b/Apostas_Diarias/Apostas_20260420.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_51B50C5595864A4B2100DEF0505ED87656CD4432" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B1E7C2-8B6A-4D99-8220-434267A1943A}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_51B50C5595864A4B2100DEF0505ED87656CD4432" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C93DB6CB-4102-4F90-9866-A07EFDFE5E46}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apostas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -333,6 +346,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -696,6 +713,20 @@
       <c r="H2">
         <v>8.6</v>
       </c>
+      <c r="I2">
+        <v>500</v>
+      </c>
+      <c r="J2" t="str">
+        <f>IF(L2=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K2">
+        <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
+        <v>61.513157894736842</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -722,6 +753,20 @@
       <c r="H3">
         <v>9.1999999999999993</v>
       </c>
+      <c r="I3">
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J62" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K62" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>57.01219512195123</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -748,6 +793,20 @@
       <c r="H4">
         <v>34</v>
       </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>14.166666666666668</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -774,6 +833,20 @@
       <c r="H5">
         <v>10</v>
       </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -800,6 +873,20 @@
       <c r="H6">
         <v>15</v>
       </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>33.392857142857146</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -826,6 +913,20 @@
       <c r="H7">
         <v>15.5</v>
       </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>32.241379310344826</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -852,6 +953,17 @@
       <c r="H8">
         <v>8</v>
       </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
       <c r="L8">
         <v>0</v>
       </c>
@@ -881,6 +993,20 @@
       <c r="H9">
         <v>13.5</v>
       </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -907,6 +1033,20 @@
       <c r="H10">
         <v>15.5</v>
       </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>32.241379310344826</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -933,6 +1073,20 @@
       <c r="H11">
         <v>14.5</v>
       </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>34.629629629629626</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -959,6 +1113,20 @@
       <c r="H12">
         <v>500</v>
       </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>0.93687374749498997</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -985,6 +1153,20 @@
       <c r="H13">
         <v>12.5</v>
       </c>
+      <c r="I13">
+        <v>500</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1011,6 +1193,20 @@
       <c r="H14">
         <v>15</v>
       </c>
+      <c r="I14">
+        <v>500</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>33.392857142857146</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1037,6 +1233,20 @@
       <c r="H15">
         <v>18.5</v>
       </c>
+      <c r="I15">
+        <v>500</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>26.714285714285715</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1063,6 +1273,20 @@
       <c r="H16">
         <v>65</v>
       </c>
+      <c r="I16">
+        <v>500</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>7.3046875</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -1089,6 +1313,20 @@
       <c r="H17">
         <v>16</v>
       </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>31.166666666666668</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1115,6 +1353,20 @@
       <c r="H18">
         <v>12</v>
       </c>
+      <c r="I18">
+        <v>500</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1141,6 +1393,20 @@
       <c r="H19">
         <v>12.5</v>
       </c>
+      <c r="I19">
+        <v>500</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1167,6 +1433,20 @@
       <c r="H20">
         <v>13</v>
       </c>
+      <c r="I20">
+        <v>500</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1193,6 +1473,20 @@
       <c r="H21">
         <v>15.5</v>
       </c>
+      <c r="I21">
+        <v>500</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>32.241379310344826</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1219,6 +1513,20 @@
       <c r="H22">
         <v>10.5</v>
       </c>
+      <c r="I22">
+        <v>500</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1245,6 +1553,20 @@
       <c r="H23">
         <v>12.5</v>
       </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1271,6 +1593,20 @@
       <c r="H24">
         <v>12.5</v>
       </c>
+      <c r="I24">
+        <v>500</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1297,6 +1633,20 @@
       <c r="H25">
         <v>12</v>
       </c>
+      <c r="I25">
+        <v>500</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1323,6 +1673,20 @@
       <c r="H26">
         <v>10</v>
       </c>
+      <c r="I26">
+        <v>500</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1349,6 +1713,20 @@
       <c r="H27">
         <v>19.5</v>
       </c>
+      <c r="I27">
+        <v>500</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>25.270270270270274</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1375,6 +1753,20 @@
       <c r="H28">
         <v>40</v>
       </c>
+      <c r="I28">
+        <v>500</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>11.987179487179489</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1401,6 +1793,20 @@
       <c r="H29">
         <v>11</v>
       </c>
+      <c r="I29">
+        <v>500</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1427,6 +1833,17 @@
       <c r="H30">
         <v>11.5</v>
       </c>
+      <c r="I30">
+        <v>500</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
       <c r="L30">
         <v>0</v>
       </c>
@@ -1456,6 +1873,20 @@
       <c r="H31">
         <v>10</v>
       </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1482,6 +1913,20 @@
       <c r="H32">
         <v>11</v>
       </c>
+      <c r="I32">
+        <v>500</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -1508,6 +1953,20 @@
       <c r="H33">
         <v>9.4</v>
       </c>
+      <c r="I33">
+        <v>500</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>55.654761904761905</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -1534,6 +1993,20 @@
       <c r="H34">
         <v>26</v>
       </c>
+      <c r="I34">
+        <v>500</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>18.700000000000003</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -1560,6 +2033,20 @@
       <c r="H35">
         <v>6.2</v>
       </c>
+      <c r="I35">
+        <v>500</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>89.90384615384616</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -1586,6 +2073,20 @@
       <c r="H36">
         <v>9.1999999999999993</v>
       </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>57.01219512195123</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -1612,6 +2113,20 @@
       <c r="H37">
         <v>15.5</v>
       </c>
+      <c r="I37">
+        <v>500</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>32.241379310344826</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -1638,6 +2153,20 @@
       <c r="H38">
         <v>23</v>
       </c>
+      <c r="I38">
+        <v>500</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>21.25</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -1664,6 +2193,20 @@
       <c r="H39">
         <v>8.4</v>
       </c>
+      <c r="I39">
+        <v>500</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>63.175675675675684</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1690,6 +2233,20 @@
       <c r="H40">
         <v>14</v>
       </c>
+      <c r="I40">
+        <v>500</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>35.96153846153846</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -1716,6 +2273,20 @@
       <c r="H41">
         <v>7.8</v>
       </c>
+      <c r="I41">
+        <v>500</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>68.75</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -1742,6 +2313,20 @@
       <c r="H42">
         <v>10</v>
       </c>
+      <c r="I42">
+        <v>500</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -1768,6 +2353,20 @@
       <c r="H43">
         <v>12</v>
       </c>
+      <c r="I43">
+        <v>500</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -1794,6 +2393,20 @@
       <c r="H44">
         <v>11.5</v>
       </c>
+      <c r="I44">
+        <v>500</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -1820,6 +2433,20 @@
       <c r="H45">
         <v>11.5</v>
       </c>
+      <c r="I45">
+        <v>500</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -1846,6 +2473,17 @@
       <c r="H46">
         <v>12.5</v>
       </c>
+      <c r="I46">
+        <v>500</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
       <c r="L46">
         <v>0</v>
       </c>
@@ -1875,6 +2513,20 @@
       <c r="H47">
         <v>9.6</v>
       </c>
+      <c r="I47">
+        <v>500</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="1"/>
+        <v>54.360465116279073</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -1901,8 +2553,22 @@
       <c r="H48">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <v>500</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="1"/>
+        <v>86.574074074074062</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -1927,8 +2593,22 @@
       <c r="H49">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <v>500</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="1"/>
+        <v>64.930555555555557</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -1953,8 +2633,22 @@
       <c r="H50">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <v>500</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="1"/>
+        <v>58.4375</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -1979,8 +2673,22 @@
       <c r="H51">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <v>500</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="1"/>
+        <v>75.403225806451616</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -2005,8 +2713,22 @@
       <c r="H52">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <v>500</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>34.629629629629626</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -2031,8 +2753,22 @@
       <c r="H53">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <v>500</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="1"/>
+        <v>73.046875</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -2057,8 +2793,22 @@
       <c r="H54">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <v>500</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="1"/>
+        <v>66.785714285714292</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2083,8 +2833,22 @@
       <c r="H55">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <v>500</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="1"/>
+        <v>59.935897435897431</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -2109,8 +2873,22 @@
       <c r="H56">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <v>500</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="1"/>
+        <v>61.513157894736842</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -2135,8 +2913,22 @@
       <c r="H57">
         <v>27</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <v>500</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="1"/>
+        <v>17.98076923076923</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -2161,8 +2953,22 @@
       <c r="H58">
         <v>8.4</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <v>500</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="1"/>
+        <v>63.175675675675684</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -2187,8 +2993,22 @@
       <c r="H59">
         <v>9</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <v>500</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="1"/>
+        <v>58.4375</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -2213,8 +3033,22 @@
       <c r="H60">
         <v>7</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <v>500</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="1"/>
+        <v>77.916666666666671</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -2239,8 +3073,22 @@
       <c r="H61">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <v>500</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -2264,6 +3112,20 @@
       </c>
       <c r="H62">
         <v>6.6</v>
+      </c>
+      <c r="I62">
+        <v>500</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="1"/>
+        <v>83.482142857142861</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Apostas_Diarias/Apostas_20260420.xlsx
+++ b/Apostas_Diarias/Apostas_20260420.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9526460E107FBEF0531510344D07F141" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C41F7E1-3FEA-46AC-A1A0-AABDC3C77BCA}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F95364F5BA501D1F050CD08366B2DF415" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F557335E-A6A4-4B32-B128-FE492FF4FBEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>Data</t>
   </si>
@@ -74,16 +74,28 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
-    <t>ENGLAND 1</t>
-  </si>
-  <si>
-    <t>Crystal Palace x West Ham</t>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>ROMANIA 1</t>
+  </si>
+  <si>
+    <t>Farul Constanta x FCSB</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Porto B x Leixoes</t>
+  </si>
+  <si>
+    <t>Sporting Lisbon B x Felgueiras</t>
   </si>
 </sst>
 </file>
@@ -423,14 +435,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -473,6 +485,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -494,12 +509,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <f>G2</f>
+        <v>10</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -508,10 +525,94 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>42.5</v>
+        <v>51.944444444444443</v>
       </c>
       <c r="L2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H4" si="0">G3</f>
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="1">$L$1</f>
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>46.75</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>11.5</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="2"/>
+        <v>RED</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Apostas_Diarias/Apostas_20260420.xlsx
+++ b/Apostas_Diarias/Apostas_20260420.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F95364F5BA501D1F050CD08366B2DF415" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F557335E-A6A4-4B32-B128-FE492FF4FBEE}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9526460E107FBEF0531510344D07F141" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C41F7E1-3FEA-46AC-A1A0-AABDC3C77BCA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Data</t>
   </si>
@@ -74,28 +74,16 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>Farul Constanta x FCSB</t>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>ENGLAND 1</t>
+  </si>
+  <si>
+    <t>Crystal Palace x West Ham</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>14:45:00</t>
-  </si>
-  <si>
-    <t>PORTUGAL 2</t>
-  </si>
-  <si>
-    <t>Porto B x Leixoes</t>
-  </si>
-  <si>
-    <t>Sporting Lisbon B x Felgueiras</t>
   </si>
 </sst>
 </file>
@@ -435,14 +423,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -485,9 +473,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -509,14 +494,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -525,94 +508,10 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>51.944444444444443</v>
+        <v>42.5</v>
       </c>
       <c r="L2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H4" si="0">G3</f>
-        <v>11</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I4" si="1">$L$1</f>
-        <v>500</v>
-      </c>
-      <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
-        <v>GREEN</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>46.75</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>11.5</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>-500</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
